--- a/en/downloads/data-excel/10.4.1.xlsx
+++ b/en/downloads/data-excel/10.4.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -323,6 +323,9 @@
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -630,14 +633,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="3" width="36.7109375" style="2" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="53.25" customHeight="1">
+    <row r="1" spans="1:18" ht="53.25" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>11</v>
       </c>
@@ -648,7 +651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="14.25" customHeight="1">
+    <row r="2" spans="1:18" ht="14.25" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -659,11 +662,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="14.25" customHeight="1" thickBot="1">
+    <row r="3" spans="1:18" ht="14.25" customHeight="1" thickBot="1">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:17" ht="17.25" customHeight="1" thickBot="1">
+    <row r="4" spans="1:18" ht="17.25" customHeight="1" thickBot="1">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -715,8 +718,11 @@
       <c r="Q4" s="7">
         <v>2023</v>
       </c>
+      <c r="R4" s="7">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="21.75" customHeight="1" thickBot="1">
+    <row r="5" spans="1:18" ht="21.75" customHeight="1" thickBot="1">
       <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
@@ -768,8 +774,11 @@
       <c r="Q5" s="8">
         <v>23.4</v>
       </c>
+      <c r="R5" s="16">
+        <v>23.1</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" customFormat="1" ht="36" customHeight="1">
+    <row r="6" spans="1:18" customFormat="1" ht="36" customHeight="1">
       <c r="A6" s="13" t="s">
         <v>12</v>
       </c>
